--- a/docentes/González Nuñez Veronica - Estadisticos 20232.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="46">
   <si>
     <t>Mat</t>
   </si>
@@ -85,52 +85,76 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>GARCIA</t>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>ANGELES</t>
+  </si>
+  <si>
+    <t>TIZA</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>LOBATO</t>
+    <t>CIRUELO</t>
   </si>
   <si>
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
     <t>PLIEGO</t>
   </si>
   <si>
-    <t>GERSON</t>
-  </si>
-  <si>
-    <t>DAVID</t>
+    <t>ROCHA</t>
+  </si>
+  <si>
+    <t>CRISTIAN OSMAR</t>
+  </si>
+  <si>
+    <t>VICTOR MANUEL</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
+    <t>MIRIAM AIMAR</t>
+  </si>
+  <si>
+    <t>ARACELY</t>
   </si>
   <si>
     <t>FABIAN ALEJANDRO</t>
   </si>
   <si>
-    <t>EMILIANO GERARDO</t>
-  </si>
-  <si>
-    <t>ARACELY</t>
-  </si>
-  <si>
     <t>JAIRO YAIR</t>
+  </si>
+  <si>
+    <t>AZURA</t>
   </si>
 </sst>
 </file>
@@ -726,16 +750,19 @@
         <v>23</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>91.3</v>
+      </c>
+      <c r="H2">
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -749,16 +776,19 @@
         <v>23</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>65.22</v>
+      </c>
+      <c r="H3">
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -772,16 +802,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>70.97</v>
+      </c>
+      <c r="H4">
+        <v>7.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -795,16 +828,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>78.95</v>
+      </c>
+      <c r="H5">
+        <v>6.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -818,16 +854,19 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>96</v>
+      </c>
+      <c r="H6">
+        <v>8.4</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -841,16 +880,19 @@
         <v>30</v>
       </c>
       <c r="D7">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>93.33</v>
+      </c>
+      <c r="H7">
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -906,16 +948,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>65.22</v>
+        <v>91.3</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -932,16 +974,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G3">
-        <v>47.83</v>
+        <v>65.22</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -958,16 +1000,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>80.65000000000001</v>
+        <v>70.97</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -993,7 +1035,7 @@
         <v>78.95</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1010,16 +1052,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G6">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H6">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1036,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G7">
-        <v>100</v>
+        <v>93.33</v>
       </c>
       <c r="H7">
         <v>8.1</v>
@@ -1055,7 +1097,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1087,16 +1129,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920183</v>
+        <v>22330051920359</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1110,16 +1152,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920188</v>
+        <v>22330051920193</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1133,22 +1175,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920413</v>
+        <v>22330051920257</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1156,22 +1198,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920205</v>
+        <v>22330051920370</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1185,10 +1227,10 @@
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1202,16 +1244,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920378</v>
+        <v>22330051920413</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1220,6 +1262,52 @@
         <v>11</v>
       </c>
       <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>22330051920378</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>22330051920230</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Nuñez Veronica - Estadisticos 20232.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="60">
   <si>
     <t>Mat</t>
   </si>
@@ -85,76 +85,118 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
+    <t>COBOS</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
+    <t>DE ROMAN</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
     <t>LOBATO</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>VERA</t>
+  </si>
+  <si>
     <t>ANGELES</t>
   </si>
   <si>
-    <t>TIZA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
+    <t>QUESADA</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>NOLASCO</t>
   </si>
   <si>
     <t>CIRUELO</t>
   </si>
   <si>
+    <t>FIERROS</t>
+  </si>
+  <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>JOSE</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
     <t>PLIEGO</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>ROCHA</t>
   </si>
   <si>
-    <t>CRISTIAN OSMAR</t>
-  </si>
-  <si>
-    <t>VICTOR MANUEL</t>
-  </si>
-  <si>
-    <t>KAREN</t>
+    <t>OLGUIN</t>
+  </si>
+  <si>
+    <t>YOLET</t>
+  </si>
+  <si>
+    <t>ARACELY</t>
+  </si>
+  <si>
+    <t>ALDO EMANUEL</t>
+  </si>
+  <si>
+    <t>FERNANDA MARGARITA</t>
+  </si>
+  <si>
+    <t>NATHALI</t>
+  </si>
+  <si>
+    <t>JONATAN GILBERTO</t>
+  </si>
+  <si>
+    <t>HECTOR MISAEL</t>
+  </si>
+  <si>
+    <t>FABIAN ALEJANDRO</t>
+  </si>
+  <si>
+    <t>JAIRO YAIR</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>AZURA</t>
+  </si>
+  <si>
+    <t>JARED DE JESUS</t>
   </si>
   <si>
     <t>MIRIAM AIMAR</t>
   </si>
   <si>
-    <t>ARACELY</t>
-  </si>
-  <si>
-    <t>FABIAN ALEJANDRO</t>
-  </si>
-  <si>
-    <t>JAIRO YAIR</t>
-  </si>
-  <si>
-    <t>AZURA</t>
+    <t>AZUL MARIAM</t>
   </si>
 </sst>
 </file>
@@ -948,16 +990,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>91.3</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -974,16 +1016,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G3">
-        <v>65.22</v>
+        <v>73.91</v>
       </c>
       <c r="H3">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1000,16 +1042,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G4">
-        <v>70.97</v>
+        <v>64.52</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1035,7 +1077,7 @@
         <v>78.95</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1061,7 +1103,7 @@
         <v>96</v>
       </c>
       <c r="H6">
-        <v>8.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1078,16 +1120,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G7">
-        <v>93.33</v>
+        <v>86.67</v>
       </c>
       <c r="H7">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1139,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1129,16 +1171,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920359</v>
+        <v>21330051920007</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1152,16 +1194,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920193</v>
+        <v>22330051920190</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1175,16 +1217,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920257</v>
+        <v>22330051920231</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1198,22 +1240,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920370</v>
+        <v>22330051920233</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1221,93 +1263,231 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920190</v>
+        <v>22330051920235</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920413</v>
+        <v>22330051920405</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920378</v>
+        <v>22330051920279</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920230</v>
+        <v>22330051920413</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920378</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920371</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920230</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>22330051920312</v>
+      </c>
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" t="s">
         <v>45</v>
       </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9">
+      <c r="D13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>22330051920370</v>
+      </c>
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>22330051920397</v>
+      </c>
+      <c r="B15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Nuñez Veronica - Estadisticos 20232.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="62">
   <si>
     <t>Mat</t>
   </si>
@@ -85,6 +85,9 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>COBOS</t>
   </si>
   <si>
@@ -155,6 +158,9 @@
   </si>
   <si>
     <t>OLGUIN</t>
+  </si>
+  <si>
+    <t>ABRAHAN</t>
   </si>
   <si>
     <t>YOLET</t>
@@ -1139,7 +1145,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1171,22 +1177,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920007</v>
+        <v>23330051920365</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1194,7 +1200,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920190</v>
+        <v>21330051920007</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
@@ -1203,7 +1209,7 @@
         <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1217,7 +1223,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920231</v>
+        <v>22330051920190</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
@@ -1226,13 +1232,13 @@
         <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1240,7 +1246,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920233</v>
+        <v>22330051920231</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
@@ -1249,7 +1255,7 @@
         <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1263,7 +1269,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920235</v>
+        <v>22330051920233</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
@@ -1272,7 +1278,7 @@
         <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1286,22 +1292,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920405</v>
+        <v>22330051920235</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1309,16 +1315,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920279</v>
+        <v>22330051920405</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1332,7 +1338,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920413</v>
+        <v>22330051920279</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
@@ -1341,21 +1347,21 @@
         <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920378</v>
+        <v>22330051920413</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
@@ -1364,7 +1370,7 @@
         <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1378,7 +1384,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920371</v>
+        <v>22330051920378</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
@@ -1387,7 +1393,7 @@
         <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -1401,7 +1407,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920230</v>
+        <v>22330051920371</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
@@ -1410,13 +1416,13 @@
         <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1424,7 +1430,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920312</v>
+        <v>22330051920230</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
@@ -1433,13 +1439,13 @@
         <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1447,16 +1453,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920370</v>
+        <v>22330051920312</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -1470,16 +1476,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920397</v>
+        <v>22330051920370</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s">
         <v>28</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -1488,6 +1494,29 @@
         <v>15</v>
       </c>
       <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>22330051920397</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Nuñez Veronica - Estadisticos 20232.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="68">
   <si>
     <t>Mat</t>
   </si>
@@ -94,33 +94,39 @@
     <t>JIMENEZ</t>
   </si>
   <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>LLANOS</t>
+  </si>
+  <si>
+    <t>DE ROMAN</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
     <t>ARELLANO</t>
   </si>
   <si>
+    <t>ANGELES</t>
+  </si>
+  <si>
     <t>BONILLA</t>
   </si>
   <si>
-    <t>DE ROMAN</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
     <t>QUESADA</t>
   </si>
   <si>
@@ -133,30 +139,36 @@
     <t>CIRUELO</t>
   </si>
   <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>JOSE</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>FIERROS</t>
   </si>
   <si>
+    <t>ROCHA</t>
+  </si>
+  <si>
     <t>IBAÑEZ</t>
   </si>
   <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>JOSE</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>ROCHA</t>
-  </si>
-  <si>
     <t>OLGUIN</t>
   </si>
   <si>
@@ -169,31 +181,37 @@
     <t>ARACELY</t>
   </si>
   <si>
+    <t>NIDIA GABRIELA</t>
+  </si>
+  <si>
+    <t>SERGIO</t>
+  </si>
+  <si>
+    <t>NATHALI</t>
+  </si>
+  <si>
+    <t>JONATAN GILBERTO</t>
+  </si>
+  <si>
+    <t>HECTOR MISAEL</t>
+  </si>
+  <si>
+    <t>FABIAN ALEJANDRO</t>
+  </si>
+  <si>
+    <t>JAIRO YAIR</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
     <t>ALDO EMANUEL</t>
   </si>
   <si>
+    <t>AZURA</t>
+  </si>
+  <si>
     <t>FERNANDA MARGARITA</t>
-  </si>
-  <si>
-    <t>NATHALI</t>
-  </si>
-  <si>
-    <t>JONATAN GILBERTO</t>
-  </si>
-  <si>
-    <t>HECTOR MISAEL</t>
-  </si>
-  <si>
-    <t>FABIAN ALEJANDRO</t>
-  </si>
-  <si>
-    <t>JAIRO YAIR</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>AZURA</t>
   </si>
   <si>
     <t>JARED DE JESUS</t>
@@ -1145,7 +1163,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1186,7 +1204,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1206,10 +1224,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1229,10 +1247,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1246,16 +1264,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920231</v>
+        <v>22330051920369</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1269,16 +1287,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920233</v>
+        <v>21330051420317</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1298,10 +1316,10 @@
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1324,7 +1342,7 @@
         <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1344,10 +1362,10 @@
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1367,10 +1385,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1390,10 +1408,10 @@
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -1413,10 +1431,10 @@
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1430,16 +1448,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920230</v>
+        <v>22330051920231</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -1453,22 +1471,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920312</v>
+        <v>22330051920230</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1476,22 +1494,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920370</v>
+        <v>22330051920233</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="D15" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1499,16 +1517,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920397</v>
+        <v>22330051920312</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -1517,6 +1535,52 @@
         <v>15</v>
       </c>
       <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>22330051920370</v>
+      </c>
+      <c r="B17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>22330051920397</v>
+      </c>
+      <c r="B18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18">
         <v>1</v>
       </c>
     </row>
